--- a/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,180 +486,252 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6.16%</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>6.51%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>+0.35%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>5899000</v>
+      </c>
       <c r="K2" t="n">
-        <v>2612000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>5979000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>世芯電子</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.52%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>255000</v>
+      </c>
       <c r="K3" t="n">
-        <v>40000</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>325000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>70,000</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>台灣玻璃工業</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.44%</t>
+        </is>
+      </c>
       <c r="J4" t="n">
-        <v>357000</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+        <v>2042000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1021000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-1,021,000</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>力旺電子</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
       <c r="J5" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>1563000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2249000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>686,000</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -671,55 +743,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
+          <t>台灣塑膠工業</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.04%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>+1.55%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>89000</v>
-      </c>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>383000</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>294,000</t>
-        </is>
-      </c>
+        <v>2612000</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -734,55 +788,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>台光電子材料</t>
-        </is>
-      </c>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.24%</t>
-        </is>
-      </c>
+          <t>世芯電子</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.76%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>+0.52%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>23000</v>
-      </c>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>9,000</t>
-        </is>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -797,55 +833,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>長榮海運</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>長榮海運</t>
-        </is>
-      </c>
+          <t>台灣玻璃工業</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.34%</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.75%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.59%</t>
-        </is>
-      </c>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>1737000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>726000</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-1,011,000</t>
-        </is>
-      </c>
+        <v>357000</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -860,55 +878,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
+          <t>力旺電子</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.64%</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.35%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>+0.71%</t>
-        </is>
-      </c>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K9" t="n">
-        <v>24000</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -933,43 +933,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>56000</v>
+        <v>89000</v>
       </c>
       <c r="K10" t="n">
-        <v>151000</v>
+        <v>383000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>294,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -996,46 +996,298 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>+0.52%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>長榮海運</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>長榮海運</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.59%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1737000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>726000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-1,011,000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>+0.71%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+1.21%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>56000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>151000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>95,000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>6446</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>藥華醫藥</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>藥華醫藥</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>1.59%</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2.02%</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>+0.43%</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J15" t="n">
         <v>108000</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K15" t="n">
         <v>138000</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>30,000</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,55 +627,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>12.71%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>11.80%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2042000</v>
+        <v>4500000</v>
       </c>
       <c r="K4" t="n">
-        <v>1021000</v>
+        <v>4200000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-1,021,000</t>
+          <t>-300,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-25_00982A_full_holdings.xlsx</t>
+          <t>2026-08-25_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,233 +685,305 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1563000</v>
+        <v>1750000</v>
       </c>
       <c r="K5" t="n">
-        <v>2249000</v>
+        <v>1700000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>686,000</t>
+          <t>-50,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-25_00982A_full_holdings.xlsx</t>
+          <t>2026-08-25_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4.35%</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.07%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>660000</v>
+      </c>
       <c r="K6" t="n">
-        <v>2612000</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>560000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>世芯電子</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.78%</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.52%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>380000</v>
+      </c>
       <c r="K7" t="n">
-        <v>40000</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>360000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>台灣玻璃工業</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.44%</t>
+        </is>
+      </c>
       <c r="J8" t="n">
-        <v>357000</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+        <v>2042000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1021000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-1,021,000</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>力旺電子</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
       <c r="J9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>1563000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2249000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>686,000</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -923,55 +995,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
+          <t>台灣塑膠工業</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.04%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>+1.55%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>89000</v>
-      </c>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>383000</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>294,000</t>
-        </is>
-      </c>
+        <v>2612000</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -986,55 +1040,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>台光電子材料</t>
-        </is>
-      </c>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1.24%</t>
-        </is>
-      </c>
+          <t>世芯電子</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.76%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>+0.52%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>23000</v>
-      </c>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>9,000</t>
-        </is>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -1049,55 +1085,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>長榮海運</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>長榮海運</t>
-        </is>
-      </c>
+          <t>台灣玻璃工業</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.34%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1.75%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.59%</t>
-        </is>
-      </c>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>1737000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>726000</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-1,011,000</t>
-        </is>
-      </c>
+        <v>357000</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -1112,55 +1130,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
+          <t>力旺電子</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.64%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1.35%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>+0.71%</t>
-        </is>
-      </c>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K13" t="n">
-        <v>24000</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -1185,43 +1185,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>56000</v>
+        <v>89000</v>
       </c>
       <c r="K14" t="n">
-        <v>151000</v>
+        <v>383000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>294,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1248,46 +1248,298 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>+0.52%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>長榮海運</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>長榮海運</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-2.59%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1737000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>726000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-1,011,000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>+0.71%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>+1.21%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>56000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>151000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>95,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>6446</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>藥華醫藥</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>藥華醫藥</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>1.59%</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2.02%</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>+0.43%</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J19" t="n">
         <v>108000</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K19" t="n">
         <v>138000</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>30,000</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,187 +990,259 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>10000000</v>
+      </c>
       <c r="K10" t="n">
-        <v>2612000</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>10358000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>358,000</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>世芯電子</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.52%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>2.93%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3040000</v>
+      </c>
       <c r="K11" t="n">
-        <v>40000</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>2880000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-160,000</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>台灣玻璃工業</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>5.44%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5.79%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>+0.35%</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>357000</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+        <v>3100000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>力旺電子</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2.33%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+        <v>4250000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4550000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1185,55 +1257,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>89000</v>
+        <v>610000</v>
       </c>
       <c r="K14" t="n">
-        <v>383000</v>
+        <v>621000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>294,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1243,60 +1315,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>23000</v>
+        <v>300000</v>
       </c>
       <c r="K15" t="n">
-        <v>32000</v>
+        <v>250000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>-50,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1306,60 +1378,60 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>長榮海運</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>長榮海運</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>3.34%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1737000</v>
+        <v>1080000</v>
       </c>
       <c r="K16" t="n">
-        <v>726000</v>
+        <v>1087000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-1,011,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1374,55 +1446,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>12000</v>
+        <v>1800000</v>
       </c>
       <c r="K17" t="n">
-        <v>24000</v>
+        <v>1900000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1437,109 +1509,730 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>56000</v>
+        <v>630000</v>
       </c>
       <c r="K18" t="n">
-        <v>151000</v>
+        <v>660000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>780000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>866000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>86,000</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1737000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>17,000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-08-25_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>00985A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>台灣塑膠工業</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>2612000</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>世芯電子</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>台灣玻璃工業</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>357000</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>力旺電子</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+1.55%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>89000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>383000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>294,000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>+0.52%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>長榮海運</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>長榮海運</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-2.59%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1737000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>726000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-1,011,000</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>+0.71%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+1.21%</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>56000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>151000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>95,000</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>6446</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>藥華醫藥</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>藥華醫藥</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>1.59%</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2.02%</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>+0.43%</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J30" t="n">
         <v>108000</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K30" t="n">
         <v>138000</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>30,000</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,259 +864,187 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.88%</t>
-        </is>
-      </c>
+          <t>台灣塑膠工業</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.44%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.44%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>2042000</v>
-      </c>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>1021000</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-1,021,000</t>
-        </is>
-      </c>
+        <v>2612000</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-25_00982A_full_holdings.xlsx</t>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5425</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>台半</t>
-        </is>
-      </c>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>台半</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
+          <t>世芯電子</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>+0.15%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1563000</v>
-      </c>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>2249000</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>686,000</t>
-        </is>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-25_00982A_full_holdings.xlsx</t>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
+          <t>台灣玻璃工業</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.12%</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.25%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>+0.13%</t>
-        </is>
-      </c>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>10358000</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>358,000</t>
-        </is>
-      </c>
+        <v>357000</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
+          <t>力旺電子</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.09%</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.93%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.16%</t>
-        </is>
-      </c>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>3040000</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2880000</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-160,000</t>
-        </is>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1131,55 +1059,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.79%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3100000</v>
+        <v>89000</v>
       </c>
       <c r="K12" t="n">
-        <v>3150000</v>
+        <v>383000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>294,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1194,55 +1122,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>台光電子材料</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>台光電子材料</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4250000</v>
+        <v>23000</v>
       </c>
       <c r="K13" t="n">
-        <v>4550000</v>
+        <v>32000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1252,60 +1180,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>長榮海運</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>長榮海運</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>610000</v>
+        <v>1737000</v>
       </c>
       <c r="K14" t="n">
-        <v>621000</v>
+        <v>726000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>-1,011,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1315,60 +1243,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>300000</v>
+        <v>12000</v>
       </c>
       <c r="K15" t="n">
-        <v>250000</v>
+        <v>24000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,55 +1311,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1080000</v>
+        <v>56000</v>
       </c>
       <c r="K16" t="n">
-        <v>1087000</v>
+        <v>151000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1446,17 +1374,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>藥華醫藥</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>藥華醫藥</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1466,773 +1394,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1800000</v>
+        <v>108000</v>
       </c>
       <c r="K17" t="n">
-        <v>1900000</v>
+        <v>138000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2.41%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2.61%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>+0.20%</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>630000</v>
-      </c>
-      <c r="K18" t="n">
-        <v>660000</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0.86%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1.02%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>+0.16%</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>780000</v>
-      </c>
-      <c r="K19" t="n">
-        <v>866000</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>86,000</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.24%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.21%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>1720000</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1737000</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>17,000</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-08-25_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>台灣塑膠工業</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>2612000</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>世芯電子</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>1.52%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>40000</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>台灣玻璃工業</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>357000</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>力旺電子</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2.04%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>+1.55%</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>89000</v>
-      </c>
-      <c r="K25" t="n">
-        <v>383000</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>294,000</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>台光電子材料</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>台光電子材料</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1.24%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1.76%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>+0.52%</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>23000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>9,000</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>長榮海運</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>長榮海運</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>4.34%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1.75%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-2.59%</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>1737000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>726000</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>-1,011,000</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0.64%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1.35%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>+0.71%</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>24000</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0.67%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>1.88%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>+1.21%</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>56000</v>
-      </c>
-      <c r="K29" t="n">
-        <v>151000</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>95,000</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>藥華醫藥</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>藥華醫藥</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1.59%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2.02%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>+0.43%</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>108000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>138000</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-26_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,90 +864,126 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2042000</v>
+      </c>
       <c r="K8" t="n">
-        <v>2612000</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>1021000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-1,021,000</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>世芯電子</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.52%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1563000</v>
+      </c>
       <c r="K9" t="n">
-        <v>40000</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>2249000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>686,000</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+          <t>2026-08-25_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -959,36 +995,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>台灣玻璃工業</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>台灣塑膠工業</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>357000</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>2612000</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
@@ -1004,36 +1040,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>力旺電子</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>世芯電子</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>40000</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
@@ -1049,55 +1085,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
+          <t>台灣玻璃工業</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2.04%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>+1.55%</t>
-        </is>
-      </c>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>89000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>383000</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>294,000</t>
-        </is>
-      </c>
+        <v>357000</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -1112,55 +1130,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>台光電子材料</t>
-        </is>
-      </c>
+          <t>力旺電子</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.24%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1.76%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>+0.52%</t>
-        </is>
-      </c>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>23000</v>
-      </c>
-      <c r="K13" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>9,000</t>
-        </is>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
@@ -1180,48 +1180,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>長榮海運</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>長榮海運</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1737000</v>
+        <v>89000</v>
       </c>
       <c r="K14" t="n">
-        <v>726000</v>
+        <v>383000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-1,011,000</t>
+          <t>294,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1248,43 +1248,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台光電子材料</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台光電子材料</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>12000</v>
+        <v>23000</v>
       </c>
       <c r="K15" t="n">
-        <v>24000</v>
+        <v>32000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1306,48 +1306,48 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>長榮海運</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>長榮海運</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>56000</v>
+        <v>1737000</v>
       </c>
       <c r="K16" t="n">
-        <v>151000</v>
+        <v>726000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>-1,011,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1374,46 +1374,172 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>+0.71%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>+1.21%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>56000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>151000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>95,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-08-25_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>6446</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>藥華醫藥</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>藥華醫藥</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>1.59%</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2.02%</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>+0.43%</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>108000</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K19" t="n">
         <v>138000</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>30,000</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-08-25_00985A_full_holdings.xlsx</t>
         </is>
